--- a/sheets/국악이꽃피는나무/검수/아름다운추억.xlsx
+++ b/sheets/국악이꽃피는나무/검수/아름다운추억.xlsx
@@ -10452,7 +10452,7 @@
       <c r="A40" s="0"/>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌r</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C40" s="26"/>

--- a/sheets/국악이꽃피는나무/검수/아름다운추억.xlsx
+++ b/sheets/국악이꽃피는나무/검수/아름다운추억.xlsx
@@ -8953,28 +8953,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="121.67" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="121.67" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="121.67" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="121.67" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
       <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="121.67" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="121.67" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="121.67" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="121.67" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="121.67" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -9399,7 +9399,7 @@
       <c r="P11" s="21"/>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="121.67" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="121.67" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="121.67" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60.61" customHeight="true">
+    <row r="16" ht="81.63" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="90.2" customHeight="true">
+    <row r="17" ht="121.67" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="90.2" customHeight="true">
+    <row r="18" ht="121.67" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="Q18" s="23"/>
     </row>
-    <row r="19" ht="90.2" customHeight="true">
+    <row r="19" ht="121.67" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="90.2" customHeight="true">
+    <row r="20" ht="121.67" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="90.2" customHeight="true">
+    <row r="21" ht="121.67" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -9778,7 +9778,7 @@
       <c r="P21" s="21"/>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="90.2" customHeight="true">
+    <row r="22" ht="121.67" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="90.2" customHeight="true">
+    <row r="23" ht="121.67" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="Q23" s="22"/>
     </row>
-    <row r="24" ht="90.2" customHeight="true">
+    <row r="24" ht="121.67" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -9915,7 +9915,7 @@
       <c r="P24" s="21"/>
       <c r="Q24" s="23"/>
     </row>
-    <row r="25" ht="90.2" customHeight="true">
+    <row r="25" ht="121.67" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="90.2" customHeight="true">
+    <row r="26" ht="121.67" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="90.2" customHeight="true">
+    <row r="27" ht="121.67" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -10015,7 +10015,7 @@
       <c r="P27" s="21"/>
       <c r="Q27" s="23"/>
     </row>
-    <row r="28" ht="90.2" customHeight="true">
+    <row r="28" ht="121.67" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
     <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60.61" customHeight="true">
+    <row r="30" ht="81.63" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
       <c r="P30" s="20"/>
       <c r="Q30" s="20"/>
     </row>
-    <row r="31" ht="90.2" customHeight="true">
+    <row r="31" ht="121.67" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
       <c r="P31" s="21"/>
       <c r="Q31" s="22"/>
     </row>
-    <row r="32" ht="90.2" customHeight="true">
+    <row r="32" ht="121.67" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
       <c r="P32" s="21"/>
       <c r="Q32" s="23"/>
     </row>
-    <row r="33" ht="90.2" customHeight="true">
+    <row r="33" ht="121.67" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="24"/>
@@ -10217,7 +10217,7 @@
       <c r="P33" s="21"/>
       <c r="Q33" s="24"/>
     </row>
-    <row r="34" ht="90.2" customHeight="true">
+    <row r="34" ht="121.67" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
       <c r="P34" s="21"/>
       <c r="Q34" s="22"/>
     </row>
-    <row r="35" ht="90.2" customHeight="true">
+    <row r="35" ht="121.67" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -10294,7 +10294,7 @@
       <c r="P35" s="21"/>
       <c r="Q35" s="23"/>
     </row>
-    <row r="36" ht="90.2" customHeight="true">
+    <row r="36" ht="121.67" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
       <c r="P36" s="21"/>
       <c r="Q36" s="24"/>
     </row>
-    <row r="37" ht="90.2" customHeight="true">
+    <row r="37" ht="121.67" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
       <c r="P37" s="21"/>
       <c r="Q37" s="22"/>
     </row>
-    <row r="38" ht="90.2" customHeight="true">
+    <row r="38" ht="121.67" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
       <c r="P38" s="21"/>
       <c r="Q38" s="23"/>
     </row>
-    <row r="39" ht="90.2" customHeight="true">
+    <row r="39" ht="121.67" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="24"/>
@@ -10448,7 +10448,7 @@
       <c r="P39" s="21"/>
       <c r="Q39" s="24"/>
     </row>
-    <row r="40" ht="90.2" customHeight="true">
+    <row r="40" ht="121.67" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="25" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
       <c r="P40" s="21"/>
       <c r="Q40" s="22"/>
     </row>
-    <row r="41" ht="90.2" customHeight="true">
+    <row r="41" ht="121.67" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="23"/>
@@ -10508,7 +10508,7 @@
       <c r="P41" s="21"/>
       <c r="Q41" s="23"/>
     </row>
-    <row r="42" ht="90.2" customHeight="true">
+    <row r="42" ht="121.67" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
     <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="60.61" customHeight="true">
+    <row r="44" ht="81.63" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
       <c r="P44" s="20"/>
       <c r="Q44" s="20"/>
     </row>
-    <row r="45" ht="90.2" customHeight="true">
+    <row r="45" ht="121.67" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="Q45" s="22"/>
     </row>
-    <row r="46" ht="90.2" customHeight="true">
+    <row r="46" ht="121.67" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21"/>
       <c r="C46" s="23"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="Q46" s="23"/>
     </row>
-    <row r="47" ht="90.2" customHeight="true">
+    <row r="47" ht="121.67" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="24"/>
@@ -10708,7 +10708,7 @@
       <c r="P47" s="21"/>
       <c r="Q47" s="24"/>
     </row>
-    <row r="48" ht="90.2" customHeight="true">
+    <row r="48" ht="121.67" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="Q48" s="22"/>
     </row>
-    <row r="49" ht="90.2" customHeight="true">
+    <row r="49" ht="121.67" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21"/>
       <c r="C49" s="23"/>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="Q49" s="23"/>
     </row>
-    <row r="50" ht="90.2" customHeight="true">
+    <row r="50" ht="121.67" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21"/>
       <c r="C50" s="24"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="Q50" s="24"/>
     </row>
-    <row r="51" ht="90.2" customHeight="true">
+    <row r="51" ht="121.67" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21"/>
       <c r="C51" s="22"/>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="Q51" s="22"/>
     </row>
-    <row r="52" ht="90.2" customHeight="true">
+    <row r="52" ht="121.67" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21"/>
       <c r="C52" s="23"/>
@@ -10914,7 +10914,7 @@
       <c r="P52" s="21"/>
       <c r="Q52" s="23"/>
     </row>
-    <row r="53" ht="90.2" customHeight="true">
+    <row r="53" ht="121.67" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="24"/>
@@ -10933,7 +10933,7 @@
       <c r="P53" s="21"/>
       <c r="Q53" s="24"/>
     </row>
-    <row r="54" ht="90.2" customHeight="true">
+    <row r="54" ht="121.67" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
@@ -10960,7 +10960,7 @@
       <c r="P54" s="21"/>
       <c r="Q54" s="22"/>
     </row>
-    <row r="55" ht="90.2" customHeight="true">
+    <row r="55" ht="121.67" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="23"/>
@@ -10987,7 +10987,7 @@
       <c r="P55" s="21"/>
       <c r="Q55" s="23"/>
     </row>
-    <row r="56" ht="90.2" customHeight="true">
+    <row r="56" ht="121.67" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21"/>
       <c r="C56" s="24"/>
@@ -11041,7 +11041,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
